--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92576565703</v>
+        <v>46157.93121730621</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93121730621</v>
+        <v>46157.9318741945</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9318741945</v>
+        <v>46157.93408207903</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93408207903</v>
+        <v>46157.93725950905</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93725950905</v>
+        <v>46158.28223481904</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28223481904</v>
+        <v>46158.29714422007</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29714422007</v>
+        <v>46158.29823796803</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29823796803</v>
+        <v>46158.33394561686</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33394561686</v>
+        <v>46158.36864285773</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кульбатырова- диспетчер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36864285773</v>
+        <v>46158.37295263974</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
